--- a/src/Tests/Tests.RunBinary_extension=xlsx.Net.verified.xlsx
+++ b/src/Tests/Tests.RunBinary_extension=xlsx.Net.verified.xlsx
@@ -8,7 +8,7 @@
     <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Basic Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Basic Data" sheetId="1" r:id="DeterministicId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
